--- a/output/pdf_financials_xlsx/GOOS.xlsx
+++ b/output/pdf_financials_xlsx/GOOS.xlsx
@@ -2082,37 +2082,37 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>9.678000000000001</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>95.3</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>31.7</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>477.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>287.7</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>286.5</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>144.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>334.4</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>408.2</v>
       </c>
     </row>
     <row r="35">
@@ -2192,37 +2192,37 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>9.678000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>95.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>31.7</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>477.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>287.7</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>286.5</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>144.9</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>334.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>408.2</v>
       </c>
     </row>
     <row r="37">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/pdf_financials_xlsx/GOOS.xlsx
+++ b/output/pdf_financials_xlsx/GOOS.xlsx
@@ -9374,7 +9374,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10518,7 +10522,11 @@
           <t>Lease liabilities 5, 13</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12946,7 +12954,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -13974,7 +13986,11 @@
           <t>Lease liabilities 4, 9</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
